--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones_Video_491_EXP5_CTRL1_36HZ.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones_Video_491_EXP5_CTRL1_36HZ.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,22 +421,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -791,302 +779,302 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1309,27 +1297,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>junto_al_borde</t>
         </is>
@@ -1384,107 +1372,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -1635,112 +1623,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>

--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones_Video_491_EXP5_CTRL1_36HZ.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones_Video_491_EXP5_CTRL1_36HZ.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cinetica_Video_491_EXP5_CTR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cin_grupos_Video_491_EXP5_C" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_491_EXP5_CTRL1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_491_EXP5_CTR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cin_grupos_Video_491_EXP5_C" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -775,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,162 +922,227 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
         </is>
       </c>
     </row>
@@ -1175,111 +1241,146 @@
           <t>0.3892-0.4058</t>
         </is>
       </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1.015199999999993</v>
       </c>
       <c r="AE2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5698358797361323</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.5632-0.5765</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="AH2" t="b">
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.5565025464027968</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5432-0.5698</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
         <v>0.3858333333333306</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>1.067500000000003</v>
       </c>
-      <c r="AK2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AN2" t="b">
-        <v>1</v>
+      <c r="AN2" t="n">
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.4665204478323792</v>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.4594-0.4737</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ2" t="b">
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
+        <v>0.4798537811657146</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.466-0.4937</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0.6483333333333361</v>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
       </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
         <v>3.1</v>
       </c>
-      <c r="AZ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.033333333333275</v>
       </c>
-      <c r="BB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2.33 s: 2 | 3.1 s: 2 | 4.65 s: 2</t>
         </is>
       </c>
-      <c r="BD2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>2 ev en k=7.781-13.785</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>0.08903012999998476</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BK2" t="n">
         <v>0.06671699999993931</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>1.33444444444543</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.1760700000000041</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.06889606261067176</v>
+      </c>
+      <c r="BQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0 contraccion(es) en 10.0 s; actividad basal 0.07 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,6 +1423,16 @@
           <t>junto_al_borde</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>en_promedio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reportable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1339,6 +1450,12 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1355,6 +1472,12 @@
       </c>
       <c r="E3" t="b">
         <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1368,244 +1491,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>384</v>
-      </c>
-      <c r="C2" t="n">
-        <v>13.01333333333333</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9731000000000449</v>
-      </c>
-      <c r="E2" t="n">
-        <v>255.5012334789002</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3808592180751274</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12.43020369119965</v>
-      </c>
-      <c r="I2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5831296421336845</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.36666666666666</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.06666666666667</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>14</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.4522326412145627</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.6666666666666696</v>
-      </c>
-      <c r="R2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13.48387606461087</v>
-      </c>
-      <c r="T2" t="n">
-        <v>33</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.053672373411223</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1008</v>
-      </c>
-      <c r="C3" t="n">
-        <v>33.96333333333334</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.057299999999941</v>
-      </c>
-      <c r="E3" t="n">
-        <v>255.3544353489148</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.4140519425696493</v>
-      </c>
-      <c r="G3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H3" t="n">
-        <v>33.40679121599476</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5565421173385801</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.4050000000000011</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.068333333333335</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.4808082544501957</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.6300000000000026</v>
-      </c>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>34.45736019824969</v>
-      </c>
-      <c r="T3" t="n">
-        <v>32</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.05056898225493</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.1760700000000041</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.06889606261067176</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0 contraccion(es) en 10.0 s; actividad basal 0.07 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1619,12 +1621,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>frame_llega_max</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tiempo_llega_max_s</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pico_dudoso_por_ruido</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>384</v>
+      </c>
+      <c r="C2" t="n">
+        <v>13.01333333333333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9731000000000449</v>
+      </c>
+      <c r="E2" t="n">
+        <v>255.5012334789002</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3808592180751274</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>384</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13.01333333333333</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12.43020369119965</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5831296421336845</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.36666666666666</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.06666666666667</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4522326412145627</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6666666666666696</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>13.48387606461087</v>
+      </c>
+      <c r="W2" t="n">
+        <v>33</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.053672373411223</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33.96333333333334</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.057299999999941</v>
+      </c>
+      <c r="E3" t="n">
+        <v>255.3544353489148</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4140519425696493</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1007</v>
+      </c>
+      <c r="I3" t="n">
+        <v>33.93666666666667</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>33.40679121599476</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5298754506719092</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4050000000000011</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.068333333333335</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5074749211168665</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6300000000000026</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>34.45736019824969</v>
+      </c>
+      <c r="W3" t="n">
+        <v>32</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05056898225493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
@@ -1650,85 +1936,105 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -1754,59 +2060,65 @@
           <t>0.3892-0.4058</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.015199999999993</v>
       </c>
       <c r="H2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5698358797361323</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5632-0.5765</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>0.5565025464027968</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5432-0.5698</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>0.3858333333333306</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1.067500000000003</v>
       </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
+      <c r="Q2" t="n">
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4665204478323792</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.4594-0.4737</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
       </c>
       <c r="U2" t="n">
+        <v>0.4798537811657146</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.466-0.4937</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.6483333333333361</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
